--- a/config/templates/material-info/label_config.xlsx
+++ b/config/templates/material-info/label_config.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="94">
   <si>
     <t>物料标签打印配置 — 修改「当前值」列后保存，刷新打印页即自动生效</t>
   </si>
@@ -84,6 +84,18 @@
     <t>名称区</t>
   </si>
   <si>
+    <t>名称字体</t>
+  </si>
+  <si>
+    <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
+  </si>
+  <si>
+    <t>顶部物料名称的字体，多个字体用英文逗号分隔</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>名称字号</t>
   </si>
   <si>
@@ -108,6 +120,12 @@
     <t>信息字段</t>
   </si>
   <si>
+    <t>字段字体</t>
+  </si>
+  <si>
+    <t>各信息字段（编号/布卡号等）的字体，多个字体用英文逗号分隔</t>
+  </si>
+  <si>
     <t>字段字号</t>
   </si>
   <si>
@@ -138,9 +156,6 @@
     <t>是 / 否</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>二维码尺寸</t>
   </si>
   <si>
@@ -181,6 +196,12 @@
   </si>
   <si>
     <t>是 / 否，控制标签底部打印时间等信息</t>
+  </si>
+  <si>
+    <t>底部字体</t>
+  </si>
+  <si>
+    <t>底部编号与打印时间的字体，多个字体用英文逗号分隔</t>
   </si>
   <si>
     <t>底部字号</t>
@@ -301,7 +322,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,13 +369,6 @@
       <color rgb="FF333333"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -867,148 +881,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1398,7 +1412,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1521,195 +1535,195 @@
       <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="11">
         <v>16</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D9" s="12">
         <v>16</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="13">
+        <v>2</v>
+      </c>
+      <c r="D10" s="14">
+        <v>2</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:6">
+      <c r="A11" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="D12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="13">
-        <v>2</v>
-      </c>
-      <c r="D9" s="14">
-        <v>2</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:6">
-      <c r="A10" s="8" t="s">
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="11">
+        <v>10</v>
+      </c>
+      <c r="D13" s="12">
+        <v>10</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="11">
-        <v>10</v>
-      </c>
-      <c r="D11" s="12">
-        <v>10</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="13">
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="13">
         <v>58</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D14" s="14">
         <v>58</v>
       </c>
-      <c r="E12" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="14" t="s">
+      <c r="E14" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:6">
+      <c r="A15" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="13">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:6">
-      <c r="A13" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="13">
+      <c r="D17" s="14">
         <v>30</v>
       </c>
-      <c r="D15" s="14">
-        <v>30</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="14" t="s">
+      <c r="E17" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1" spans="1:6">
-      <c r="A16" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="11">
-        <v>1</v>
-      </c>
-      <c r="D17" s="12">
-        <v>1</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
     <row r="18" ht="18" customHeight="1" spans="1:6">
-      <c r="A18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="13">
-        <v>4</v>
-      </c>
-      <c r="D18" s="14">
-        <v>4</v>
-      </c>
-      <c r="E18" s="14" t="s">
+      <c r="A18" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="14" t="s">
-        <v>11</v>
-      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="10"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="11">
         <v>1</v>
@@ -1718,100 +1732,160 @@
         <v>1</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:6">
-      <c r="A20" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="10"/>
+      <c r="A20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="13">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14">
+        <v>4</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:6">
       <c r="A21" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>34</v>
+        <v>50</v>
+      </c>
+      <c r="C21" s="11">
+        <v>1</v>
+      </c>
+      <c r="D21" s="12">
+        <v>1</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:6">
-      <c r="A22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="13">
+      <c r="A22" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:6">
+      <c r="A23" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" ht="80" spans="1:6">
+      <c r="A24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="13">
+        <v>9</v>
+      </c>
+      <c r="D25" s="14">
         <v>7</v>
       </c>
-      <c r="D22" s="14">
-        <v>7</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:6">
-      <c r="A23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="E25" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" ht="40" spans="1:6">
+      <c r="A26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:6">
-      <c r="A24" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>36</v>
+      <c r="B26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" ht="27" spans="1:6">
+      <c r="A27" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1842,32 +1916,32 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -1875,13 +1949,13 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D4" s="5">
         <v>2</v>
@@ -1889,13 +1963,13 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -1903,13 +1977,13 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5">
         <v>4</v>
@@ -1917,13 +1991,13 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D7" s="3">
         <v>5</v>
@@ -1931,13 +2005,13 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D8" s="5">
         <v>6</v>
@@ -1945,13 +2019,13 @@
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3">
         <v>7</v>
@@ -1959,13 +2033,13 @@
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D10" s="5">
         <v>8</v>
@@ -1973,13 +2047,13 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D11" s="3">
         <v>9</v>
@@ -1987,13 +2061,13 @@
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:4">
       <c r="A12" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="D12" s="5">
         <v>10</v>
@@ -2001,13 +2075,13 @@
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D13" s="3">
         <v>11</v>

--- a/config/templates/material-info/label_config.xlsx
+++ b/config/templates/material-info/label_config.xlsx
@@ -1193,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1519,293 +1519,289 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>字段内容最多行数</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>普通字段内容超出行数时自动截断，0 = 不限制</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>行</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>信息字段</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>备注最多行数</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C15" t="n">
         <v>4</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>备注内容超出行数时自动截断，0 = 不限制</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>行</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>信息字段</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>标签列宽</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C16" s="13" t="n">
         <v>58</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D16" s="14" t="n">
         <v>58</v>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>字段标签文字（如"物料编号"）的列宽</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  【二维码】</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>二维码</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>显示二维码</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>是 / 否</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>二维码</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>二维码尺寸</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C19" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D19" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>二维码图片边长</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  【批量打印布局】</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>批量打印</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>每行标签数</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C21" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>批量打印时每行排列几张标签</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>批量打印</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>标签间距</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>4</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>4</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>相邻标签之间的间隙</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>批量打印</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>每页标签数</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C23" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>超过此数量后自动换页（0 = 不限制）</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  【底部信息】</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="80" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>底部信息</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>显示底部信息</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>是 / 否，控制标签底部打印时间等信息</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>底部信息</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>底部字体</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>底部编号与打印时间的字体，多个字体用英文逗号分隔</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1819,23 +1815,27 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>底部字号</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>7</v>
+          <t>底部字体</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
+        </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>底部编号与打印时间的字体大小</t>
+          <t>底部编号与打印时间的字体，多个字体用英文逗号分隔</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1847,57 +1847,85 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>底部字号</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>底部编号与打印时间的字体大小</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>底部信息</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
           <t>底部左侧内容</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>厦门吉信德集团有限公司</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>{material_code}</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>支持占位符：{material_code}、{material_name}、{print_time} 等</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>底部信息</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>底部右侧内容</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>{print_time}</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>{print_time}</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>支持占位符：{material_code}、{material_name}、{print_time} 等</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1905,13 +1933,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/templates/material-info/label_config.xlsx
+++ b/config/templates/material-info/label_config.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="31">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -209,8 +209,36 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="001A6FC4"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="001A6FC4"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="41">
     <fill>
       <patternFill/>
     </fill>
@@ -427,8 +455,28 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A6FC4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8ECF0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -593,6 +641,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -741,7 +803,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -779,6 +841,34 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1193,8 +1283,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -1205,741 +1295,874 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>物料标签打印配置 — 修改「当前值」列后保存，刷新打印页即自动生效</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>参数分组</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>参数名称</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>当前值</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>默认值</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  【模板信息】</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="18" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>模板信息</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>模板名称</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>标准模板</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>标准模板</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>打印页展示的模板名称</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>模板信息</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>布局类型</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>standard = 标准标签；split_2 = 一张纸分成两个信息区</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  【标签尺寸】</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="10" t="n"/>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>标签尺寸</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>标签宽度</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C7" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D7" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>标签纸宽度</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>标签尺寸</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>标签最小高度</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C8" s="23" t="n">
         <v>87</v>
       </c>
-      <c r="D5" s="14" t="n">
-        <v>87</v>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="D8" s="24" t="n">
+        <v>58</v>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>标签内容不足时的最小高度，内容超出时自动撑高</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>标签尺寸</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>内边距</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C9" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D9" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>标签四边内部留白</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  【名称区】</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>名称区</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>名称字体</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>顶部物料名称的字体，多个字体用英文逗号分隔</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>名称区</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>名称字号</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>顶部物料名称的字体大小</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>名称区</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>名称最多行数</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>超出行数时自动截断</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>行</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  【信息字段】</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>信息字段</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>字段字体</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>各信息字段（编号/布卡号等）的字体，多个字体用英文逗号分隔</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>信息字段</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>字段字号</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>各信息字段（编号/布卡号等）的字体大小</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>信息字段</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>字段标签字号</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>字段标签文字（如物料编码、颜色）的字体大小</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>信息字段</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>字段内容最多行数</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>普通字段内容超出行数时自动截断，0 = 不限制</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>行</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>信息字段</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>颜色最多行数</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>颜色字段内容超出行数时自动截断，0 = 不限制</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>行</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>信息字段</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>备注最多行数</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>备注内容超出行数时自动截断，0 = 不限制</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>行</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>信息字段</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>标签列宽</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>字段标签文字（如"物料编号"）的列宽</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  【二维码】</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>二维码</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>显示二维码</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>是 / 否</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>二维码</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>二维码尺寸</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="D24" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>二维码图片边长</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  【批量打印布局】</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>批量打印</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>每行标签数</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>批量打印时每行排列几张标签</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>批量打印</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>标签间距</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>标签四边内部留白</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>相邻标签之间的间隙</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  【名称区】</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="10" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>名称区</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>名称字体</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>批量打印</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>每页标签数</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>超过此数量后自动换页（0 = 不限制）</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  【底部信息】</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>底部信息</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>显示底部信息</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>是 / 否，控制标签底部打印时间等信息</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>底部信息</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>底部字体</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>顶部物料名称的字体，多个字体用英文逗号分隔</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>底部编号与打印时间的字体，多个字体用英文逗号分隔</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>名称区</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>名称字号</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>顶部物料名称的字体大小</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>底部信息</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>底部字号</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>底部编号与打印时间的字体大小</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>名称区</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>名称最多行数</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>超出行数时自动截断</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>行</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  【信息字段】</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="10" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>信息字段</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>字段字体</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>各信息字段（编号/布卡号等）的字体，多个字体用英文逗号分隔</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>底部信息</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>底部左侧内容</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>厦门吉信德集团有限公司</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>{material_code}</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>支持占位符：{material_code}、{material_name}、{print_time} 等</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>信息字段</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>字段字号</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>各信息字段（编号/布卡号等）的字体大小</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>pt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>信息字段</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>字段内容最多行数</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>普通字段内容超出行数时自动截断，0 = 不限制</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>行</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>信息字段</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>备注最多行数</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注内容超出行数时自动截断，0 = 不限制</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>行</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>信息字段</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>标签列宽</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>58</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>58</v>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>字段标签文字（如"物料编号"）的列宽</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  【二维码】</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>二维码</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>显示二维码</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>是 / 否</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>底部信息</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>底部右侧内容</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>{print_time}</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>{print_time}</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>支持占位符：{material_code}、{material_name}、{print_time} 等</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>二维码</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>二维码尺寸</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>二维码图片边长</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  【批量打印布局】</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>批量打印</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>每行标签数</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>批量打印时每行排列几张标签</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>批量打印</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>标签间距</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>相邻标签之间的间隙</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>批量打印</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>每页标签数</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>超过此数量后自动换页（0 = 不限制）</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="80" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  【底部信息】</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>底部信息</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>显示底部信息</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>是 / 否，控制标签底部打印时间等信息</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>底部信息</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>底部字体</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>底部编号与打印时间的字体，多个字体用英文逗号分隔</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>底部信息</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>底部字号</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>底部编号与打印时间的字体大小</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>pt</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>底部信息</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>底部左侧内容</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>厦门吉信德集团有限公司</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>{material_code}</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>支持占位符：{material_code}、{material_name}、{print_time} 等</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>底部信息</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>底部右侧内容</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>{print_time}</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>{print_time}</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>支持占位符：{material_code}、{material_name}、{print_time} 等</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="8">
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
